--- a/service_feedback_forms/029_restaurant_feedback_form--service_feedback_forms.xlsx
+++ b/service_feedback_forms/029_restaurant_feedback_form--service_feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'text':_'very_likely'}</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'text': 'Very likely'}</t>
+          <t>Very likely</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'text':_'likely'}</t>
+          <t>likely</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'text': 'Likely'}</t>
+          <t>Likely</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'text':_'not_likely'}</t>
+          <t>not_likely</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'text': 'Not likely'}</t>
+          <t>Not likely</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'text':_'not_at_all_likely'}</t>
+          <t>not_at_all_likely</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'text': 'Not at all likely'}</t>
+          <t>Not at all likely</t>
         </is>
       </c>
     </row>
